--- a/ResourcesPK/section_bulk_file.xlsx
+++ b/ResourcesPK/section_bulk_file.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -48,25 +48,19 @@
     <t>C0100002014</t>
   </si>
   <si>
-    <t>C0124176746</t>
-  </si>
-  <si>
     <t>C0124176760</t>
   </si>
   <si>
-    <t>C0124176766</t>
-  </si>
-  <si>
     <t>Test Outlet 1</t>
   </si>
   <si>
-    <t>Test Outlet 2</t>
-  </si>
-  <si>
     <t>Test Outlet 3</t>
   </si>
   <si>
-    <t>Test Outlet 4</t>
+    <t>TMP00111871</t>
+  </si>
+  <si>
+    <t>AKRAM K/S</t>
   </si>
 </sst>
 </file>
@@ -384,7 +378,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
@@ -425,7 +419,7 @@
         <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -442,7 +436,7 @@
         <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
@@ -456,27 +450,10 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesPK/section_bulk_file.xlsx
+++ b/ResourcesPK/section_bulk_file.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>Distributor Code</t>
   </si>
@@ -39,9 +39,6 @@
     <t>50250327</t>
   </si>
   <si>
-    <t>571625412415</t>
-  </si>
-  <si>
     <t>Hassan Sec</t>
   </si>
   <si>
@@ -57,16 +54,95 @@
     <t>Test Outlet 3</t>
   </si>
   <si>
-    <t>TMP00111871</t>
-  </si>
-  <si>
-    <t>AKRAM K/S</t>
+    <t>AUTOSECFBD7</t>
+  </si>
+  <si>
+    <t>AUTOSECF06B</t>
+  </si>
+  <si>
+    <t>AUTOSEC4A4D</t>
+  </si>
+  <si>
+    <t>AUTOSEC5A61</t>
+  </si>
+  <si>
+    <t>AUTOSEC1C7A</t>
+  </si>
+  <si>
+    <t>AUTOSEC8A4D</t>
+  </si>
+  <si>
+    <t>AUTOSECEF19</t>
+  </si>
+  <si>
+    <t>AUTOSEC67F3</t>
+  </si>
+  <si>
+    <t>AUTOSEC30D5</t>
+  </si>
+  <si>
+    <t>AUTOSECB7DA</t>
+  </si>
+  <si>
+    <t>AUTOSEC7EC1</t>
+  </si>
+  <si>
+    <t>AUTOSECDBDA</t>
+  </si>
+  <si>
+    <t>AUTOSEC32B3</t>
+  </si>
+  <si>
+    <t>AUTOSEC04A6</t>
+  </si>
+  <si>
+    <t>AUTOSECA02C</t>
+  </si>
+  <si>
+    <t>AUTOSEC0F3A</t>
+  </si>
+  <si>
+    <t>AUTOSECEA8C</t>
+  </si>
+  <si>
+    <t>AUTOSEC8972</t>
+  </si>
+  <si>
+    <t>AUTOSECE9EA</t>
+  </si>
+  <si>
+    <t>AUTOSEC0808</t>
+  </si>
+  <si>
+    <t>AUTOSEC8358</t>
+  </si>
+  <si>
+    <t>AUTOSEC024B</t>
+  </si>
+  <si>
+    <t>AUTOSECA1D6</t>
+  </si>
+  <si>
+    <t>AUTOSEC3244</t>
+  </si>
+  <si>
+    <t>AUTOSEC35B5</t>
+  </si>
+  <si>
+    <t>AUTOSEC19AE</t>
+  </si>
+  <si>
+    <t>AUTOSEC4498</t>
+  </si>
+  <si>
+    <t>AUTOSEC3889</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -96,8 +172,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -378,82 +455,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="15.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.1796875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.453125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.1796875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="29.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
+      <c r="E2" t="s" s="0">
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
+      <c r="D3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
